--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>112680534</v>
       </c>
       <c r="B2" t="n">
-        <v>85599</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,7 +724,7 @@
         <v>728283</v>
       </c>
       <c r="R2" t="n">
-        <v>6371839</v>
+        <v>6371840</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -794,56 +789,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112680545</v>
+        <v>113868234</v>
       </c>
       <c r="B3" t="n">
-        <v>89288</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3286</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mattsarve, Gtl</t>
+          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>728433</v>
+        <v>728342</v>
       </c>
       <c r="R3" t="n">
-        <v>6371706</v>
+        <v>6371738</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,27 +886,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingrid Thomasson</t>
+          <t>Cecilia Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113869302</v>
+        <v>112680545</v>
       </c>
       <c r="B4" t="n">
-        <v>86215</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,48 +909,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>3286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelgarn Mattsarve vid Uppstaig, Gtl</t>
+          <t>Mattsarve, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>728213</v>
+        <v>728433</v>
       </c>
       <c r="R4" t="n">
-        <v>6371873</v>
+        <v>6371706</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,12 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,59 +987,54 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Nygren</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113868213</v>
+        <v>113868322</v>
       </c>
       <c r="B5" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>3286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1065,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>728342</v>
+        <v>728207</v>
       </c>
       <c r="R5" t="n">
-        <v>6371738</v>
+        <v>6371872</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,15 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113869518</v>
+        <v>113868403</v>
       </c>
       <c r="B6" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1168,11 +1143,10 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>728379</v>
+        <v>728213</v>
       </c>
       <c r="R6" t="n">
-        <v>6371711</v>
+        <v>6371873</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1246,16 +1220,11 @@
         <v>113868297</v>
       </c>
       <c r="B7" t="n">
-        <v>86048</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1357,47 +1326,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113868403</v>
+        <v>113868213</v>
       </c>
       <c r="B8" t="n">
-        <v>86180</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1408,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>728213</v>
+        <v>728342</v>
       </c>
       <c r="R8" t="n">
-        <v>6371873</v>
+        <v>6371738</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1471,15 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113868234</v>
+        <v>113869483</v>
       </c>
       <c r="B9" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,34 +1446,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1522,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>728342</v>
+        <v>728401</v>
       </c>
       <c r="R9" t="n">
-        <v>6371738</v>
+        <v>6371719</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1585,37 +1545,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113868322</v>
+        <v>113869518</v>
       </c>
       <c r="B10" t="n">
-        <v>89815</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3286</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1625,10 +1580,11 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1636,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>728207</v>
+        <v>728379</v>
       </c>
       <c r="R10" t="n">
-        <v>6371872</v>
+        <v>6371711</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1699,51 +1655,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113869483</v>
+        <v>113869302</v>
       </c>
       <c r="B11" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1751,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>728401</v>
+        <v>728213</v>
       </c>
       <c r="R11" t="n">
-        <v>6371719</v>
+        <v>6371873</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1817,12 +1767,7 @@
         <v>113869505</v>
       </c>
       <c r="B12" t="n">
-        <v>86183</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39376-2023 artfynd.xlsx
+++ b/artfynd/A 39376-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112680534</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113868234</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112680545</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113868322</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113868403</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113868297</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113868213</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113869483</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113869518</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1761,6 +1811,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113869302</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,8 +1925,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113869505</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>